--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -1078,7 +1078,7 @@
     <t>0.0004,0.9687,0.7947,0.0004</t>
   </si>
   <si>
-    <t>0.0002,0.8538,0.9907,0.0001</t>
+    <t>0.0002,0.8537,0.9907,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9932,0.9775,0.0000</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="528">
   <si>
     <t>Filename</t>
   </si>
@@ -817,6 +817,9 @@
     <t>0,0,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,0</t>
   </si>
   <si>
@@ -826,6 +829,12 @@
     <t>0,1,0,1</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0.9610,0.0046,0.0112,0.0013</t>
   </si>
   <si>
@@ -835,7 +844,7 @@
     <t>0.8693,0.0034,0.0004,0.0523</t>
   </si>
   <si>
-    <t>0.3263,0.0011,0.0016,0.6273</t>
+    <t>0.3268,0.0011,0.0016,0.6266</t>
   </si>
   <si>
     <t>0.9923,0.0024,0.0012,0.0005</t>
@@ -859,22 +868,22 @@
     <t>0.9954,0.0015,0.0005,0.0002</t>
   </si>
   <si>
-    <t>0.9931,0.0019,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.8046,0.0115,0.1629,0.0022</t>
-  </si>
-  <si>
-    <t>0.0164,0.0795,0.9355,0.0024</t>
-  </si>
-  <si>
-    <t>0.1100,0.0011,0.9301,0.0003</t>
+    <t>0.9931,0.0019,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.8048,0.0115,0.1627,0.0022</t>
+  </si>
+  <si>
+    <t>0.0163,0.0796,0.9355,0.0024</t>
+  </si>
+  <si>
+    <t>0.1102,0.0011,0.9300,0.0003</t>
   </si>
   <si>
     <t>0.0607,0.0060,0.9477,0.0013</t>
   </si>
   <si>
-    <t>0.5132,0.0016,0.5480,0.0005</t>
+    <t>0.5134,0.0016,0.5478,0.0005</t>
   </si>
   <si>
     <t>0.0011,0.9989,0.0054,0.0002</t>
@@ -883,7 +892,7 @@
     <t>0.0021,0.9970,0.0029,0.0010</t>
   </si>
   <si>
-    <t>0.1730,0.9388,0.0024,0.0000</t>
+    <t>0.1729,0.9388,0.0024,0.0000</t>
   </si>
   <si>
     <t>0.0033,0.9950,0.0073,0.0023</t>
@@ -892,10 +901,10 @@
     <t>0.0013,0.9992,0.0249,0.0000</t>
   </si>
   <si>
-    <t>0.4200,0.0007,0.6805,0.0008</t>
-  </si>
-  <si>
-    <t>0.0741,0.0100,0.9278,0.0060</t>
+    <t>0.4200,0.0007,0.6806,0.0008</t>
+  </si>
+  <si>
+    <t>0.0741,0.0100,0.9278,0.0059</t>
   </si>
   <si>
     <t>0.0157,0.0002,0.9923,0.0001</t>
@@ -904,40 +913,40 @@
     <t>0.0126,0.0032,0.9875,0.0007</t>
   </si>
   <si>
-    <t>0.0163,0.0010,0.9882,0.0007</t>
-  </si>
-  <si>
-    <t>0.0514,0.0007,0.9686,0.0004</t>
+    <t>0.0163,0.0010,0.9881,0.0007</t>
+  </si>
+  <si>
+    <t>0.0515,0.0007,0.9686,0.0004</t>
   </si>
   <si>
     <t>0.0090,0.0005,0.9932,0.0003</t>
   </si>
   <si>
-    <t>0.6409,0.4297,0.0296,0.0011</t>
-  </si>
-  <si>
-    <t>0.9393,0.0701,0.0061,0.0010</t>
+    <t>0.6411,0.4293,0.0296,0.0011</t>
+  </si>
+  <si>
+    <t>0.9392,0.0702,0.0061,0.0010</t>
   </si>
   <si>
     <t>0.0014,0.0001,0.9987,0.0002</t>
   </si>
   <si>
-    <t>0.0166,0.3097,0.8506,0.0015</t>
-  </si>
-  <si>
-    <t>0.9341,0.0019,0.0467,0.0007</t>
-  </si>
-  <si>
-    <t>0.8549,0.0061,0.1126,0.0014</t>
-  </si>
-  <si>
-    <t>0.3516,0.8142,0.0111,0.0005</t>
-  </si>
-  <si>
-    <t>0.0218,0.9525,0.3600,0.0034</t>
-  </si>
-  <si>
-    <t>0.0005,0.8784,0.9646,0.0001</t>
+    <t>0.0166,0.3096,0.8506,0.0015</t>
+  </si>
+  <si>
+    <t>0.9343,0.0019,0.0466,0.0007</t>
+  </si>
+  <si>
+    <t>0.8551,0.0061,0.1124,0.0014</t>
+  </si>
+  <si>
+    <t>0.3517,0.8141,0.0111,0.0005</t>
+  </si>
+  <si>
+    <t>0.0218,0.9525,0.3594,0.0034</t>
+  </si>
+  <si>
+    <t>0.0005,0.8785,0.9645,0.0001</t>
   </si>
   <si>
     <t>0.0013,0.0047,0.9960,0.0036</t>
@@ -946,19 +955,19 @@
     <t>0.0291,0.0241,0.9493,0.0098</t>
   </si>
   <si>
-    <t>0.0679,0.0007,0.8756,0.0520</t>
-  </si>
-  <si>
-    <t>0.0011,0.9348,0.8107,0.0006</t>
+    <t>0.0679,0.0007,0.8754,0.0521</t>
+  </si>
+  <si>
+    <t>0.0011,0.9349,0.8102,0.0006</t>
   </si>
   <si>
     <t>0.0004,0.9963,0.0070,0.0009</t>
   </si>
   <si>
-    <t>0.0043,0.0111,0.9911,0.0012</t>
-  </si>
-  <si>
-    <t>0.0006,0.6536,0.0010,0.9742</t>
+    <t>0.0043,0.0111,0.9910,0.0012</t>
+  </si>
+  <si>
+    <t>0.0006,0.6539,0.0010,0.9741</t>
   </si>
   <si>
     <t>0.0001,0.9997,0.0002,0.0001</t>
@@ -973,7 +982,7 @@
     <t>0.0011,0.0176,0.9938,0.0016</t>
   </si>
   <si>
-    <t>0.0008,0.0833,0.9927,0.0012</t>
+    <t>0.0008,0.0834,0.9927,0.0012</t>
   </si>
   <si>
     <t>0.0092,0.0017,0.9899,0.0008</t>
@@ -988,16 +997,16 @@
     <t>0.0211,0.0105,0.9710,0.0024</t>
   </si>
   <si>
-    <t>0.9717,0.0141,0.0077,0.0005</t>
-  </si>
-  <si>
-    <t>0.9846,0.0012,0.0065,0.0003</t>
-  </si>
-  <si>
-    <t>0.9765,0.0116,0.0042,0.0014</t>
-  </si>
-  <si>
-    <t>0.4506,0.0007,0.5647,0.0007</t>
+    <t>0.9717,0.0141,0.0076,0.0005</t>
+  </si>
+  <si>
+    <t>0.9846,0.0012,0.0064,0.0003</t>
+  </si>
+  <si>
+    <t>0.9766,0.0116,0.0042,0.0014</t>
+  </si>
+  <si>
+    <t>0.4506,0.0007,0.5645,0.0007</t>
   </si>
   <si>
     <t>0.9854,0.0010,0.0065,0.0004</t>
@@ -1006,16 +1015,16 @@
     <t>0.9905,0.0021,0.0023,0.0006</t>
   </si>
   <si>
-    <t>0.9872,0.0012,0.0048,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9979,0.9036,0.0000</t>
+    <t>0.9872,0.0012,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9979,0.9034,0.0000</t>
   </si>
   <si>
     <t>0.0012,0.0142,0.9977,0.0001</t>
   </si>
   <si>
-    <t>0.0035,0.0355,0.9904,0.0017</t>
+    <t>0.0035,0.0356,0.9904,0.0017</t>
   </si>
   <si>
     <t>0.0002,0.9756,0.9565,0.0002</t>
@@ -1030,25 +1039,25 @@
     <t>0.0003,0.9994,0.0033,0.0000</t>
   </si>
   <si>
-    <t>0.9687,0.0014,0.0212,0.0003</t>
-  </si>
-  <si>
-    <t>0.2567,0.1202,0.5486,0.0026</t>
-  </si>
-  <si>
-    <t>0.0064,0.0043,0.9910,0.0008</t>
+    <t>0.9687,0.0014,0.0213,0.0003</t>
+  </si>
+  <si>
+    <t>0.2573,0.1200,0.5480,0.0026</t>
+  </si>
+  <si>
+    <t>0.0064,0.0042,0.9910,0.0008</t>
   </si>
   <si>
     <t>0.0002,0.9749,0.9617,0.0001</t>
   </si>
   <si>
-    <t>0.0003,0.9522,0.9728,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9990,0.3409,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9600,0.9627,0.0003</t>
+    <t>0.0003,0.9524,0.9728,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.3403,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9601,0.9626,0.0003</t>
   </si>
   <si>
     <t>0.0011,0.0020,0.0009,0.9997</t>
@@ -1069,28 +1078,28 @@
     <t>0.0002,0.0010,0.0007,0.9999</t>
   </si>
   <si>
-    <t>0.0004,0.9975,0.4710,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.8919,0.9786,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9687,0.7947,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.8537,0.9907,0.0001</t>
+    <t>0.0004,0.9975,0.4704,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.8921,0.9786,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9687,0.7942,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.8540,0.9906,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9932,0.9775,0.0000</t>
   </si>
   <si>
-    <t>0.0007,0.9897,0.5075,0.0002</t>
-  </si>
-  <si>
-    <t>0.9925,0.0060,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9712,0.0188,0.0038,0.0010</t>
+    <t>0.0007,0.9898,0.5068,0.0002</t>
+  </si>
+  <si>
+    <t>0.9925,0.0059,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9713,0.0188,0.0038,0.0009</t>
   </si>
   <si>
     <t>0.9497,0.0785,0.0016,0.0003</t>
@@ -1105,13 +1114,13 @@
     <t>0.9847,0.0118,0.0025,0.0020</t>
   </si>
   <si>
-    <t>0.9713,0.0045,0.0109,0.0014</t>
+    <t>0.9712,0.0045,0.0109,0.0014</t>
   </si>
   <si>
     <t>0.9813,0.0057,0.0029,0.0004</t>
   </si>
   <si>
-    <t>0.9934,0.0019,0.0010,0.0005</t>
+    <t>0.9933,0.0019,0.0010,0.0005</t>
   </si>
   <si>
     <t>0.9888,0.0102,0.0013,0.0007</t>
@@ -1126,13 +1135,13 @@
     <t>0.9839,0.0068,0.0023,0.0020</t>
   </si>
   <si>
-    <t>0.9940,0.0046,0.0008,0.0007</t>
+    <t>0.9941,0.0046,0.0008,0.0007</t>
   </si>
   <si>
     <t>0.9941,0.0029,0.0006,0.0005</t>
   </si>
   <si>
-    <t>0.9933,0.0020,0.0010,0.0004</t>
+    <t>0.9933,0.0019,0.0010,0.0004</t>
   </si>
   <si>
     <t>0.0007,0.0001,0.9995,0.0000</t>
@@ -1141,7 +1150,7 @@
     <t>0.0451,0.0030,0.9637,0.0016</t>
   </si>
   <si>
-    <t>0.9318,0.0003,0.1003,0.0001</t>
+    <t>0.9317,0.0003,0.1005,0.0001</t>
   </si>
   <si>
     <t>0.0336,0.0012,0.9778,0.0006</t>
@@ -1153,10 +1162,10 @@
     <t>0.0002,0.9998,0.0007,0.0000</t>
   </si>
   <si>
-    <t>0.5050,0.6667,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.1737,0.9045,0.0086,0.0009</t>
+    <t>0.5046,0.6670,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.1735,0.9046,0.0087,0.0009</t>
   </si>
   <si>
     <t>0.0005,0.9995,0.0006,0.0001</t>
@@ -1165,22 +1174,22 @@
     <t>0.0000,0.9999,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.8863,0.2150,0.0054,0.0003</t>
-  </si>
-  <si>
-    <t>0.2022,0.0239,0.7832,0.0060</t>
-  </si>
-  <si>
-    <t>0.0700,0.0091,0.9301,0.0055</t>
-  </si>
-  <si>
-    <t>0.4626,0.0094,0.5368,0.0014</t>
-  </si>
-  <si>
-    <t>0.1983,0.0163,0.8111,0.0078</t>
-  </si>
-  <si>
-    <t>0.0008,0.7641,0.7959,0.0996</t>
+    <t>0.8864,0.2146,0.0054,0.0003</t>
+  </si>
+  <si>
+    <t>0.2026,0.0239,0.7828,0.0060</t>
+  </si>
+  <si>
+    <t>0.0702,0.0091,0.9299,0.0055</t>
+  </si>
+  <si>
+    <t>0.4631,0.0094,0.5363,0.0014</t>
+  </si>
+  <si>
+    <t>0.1982,0.0163,0.8112,0.0078</t>
+  </si>
+  <si>
+    <t>0.0008,0.7644,0.7957,0.0996</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0015,0.0000</t>
@@ -1195,13 +1204,13 @@
     <t>0.0002,0.9987,0.0120,0.0006</t>
   </si>
   <si>
-    <t>0.0025,0.9968,0.1543,0.0002</t>
-  </si>
-  <si>
-    <t>0.3771,0.6326,0.0719,0.0024</t>
-  </si>
-  <si>
-    <t>0.0427,0.9579,0.0305,0.0054</t>
+    <t>0.0025,0.9968,0.1544,0.0002</t>
+  </si>
+  <si>
+    <t>0.3773,0.6324,0.0719,0.0024</t>
+  </si>
+  <si>
+    <t>0.0427,0.9579,0.0306,0.0054</t>
   </si>
   <si>
     <t>0.9956,0.0004,0.0010,0.0002</t>
@@ -1228,10 +1237,10 @@
     <t>0.9930,0.0008,0.0016,0.0005</t>
   </si>
   <si>
-    <t>0.0007,0.9591,0.9183,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.6270,0.9949,0.0000</t>
+    <t>0.0007,0.9592,0.9182,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.6272,0.9949,0.0000</t>
   </si>
   <si>
     <t>0.0005,0.0305,0.9982,0.0004</t>
@@ -1243,13 +1252,13 @@
     <t>0.9521,0.0021,0.0353,0.0004</t>
   </si>
   <si>
-    <t>0.3069,0.4496,0.1146,0.0079</t>
-  </si>
-  <si>
-    <t>0.1449,0.0005,0.9052,0.0009</t>
-  </si>
-  <si>
-    <t>0.6585,0.0102,0.3205,0.0031</t>
+    <t>0.3070,0.4495,0.1145,0.0079</t>
+  </si>
+  <si>
+    <t>0.1451,0.0005,0.9051,0.0009</t>
+  </si>
+  <si>
+    <t>0.6580,0.0102,0.3211,0.0031</t>
   </si>
   <si>
     <t>0.0032,0.0001,0.0006,0.9994</t>
@@ -1264,13 +1273,13 @@
     <t>0.0020,0.0003,0.0006,0.9997</t>
   </si>
   <si>
-    <t>0.0002,0.9888,0.9047,0.0001</t>
+    <t>0.0002,0.9888,0.9046,0.0001</t>
   </si>
   <si>
     <t>0.9818,0.0011,0.0078,0.0007</t>
   </si>
   <si>
-    <t>0.0325,0.9699,0.0103,0.0032</t>
+    <t>0.0325,0.9698,0.0103,0.0032</t>
   </si>
   <si>
     <t>0.9886,0.0008,0.0042,0.0004</t>
@@ -1285,34 +1294,34 @@
     <t>0.0806,0.0000,0.9665,0.0000</t>
   </si>
   <si>
-    <t>0.0719,0.0001,0.9577,0.0000</t>
+    <t>0.0719,0.0001,0.9576,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8439,0.0006,0.1048,0.0076</t>
+    <t>0.8441,0.0006,0.1046,0.0076</t>
   </si>
   <si>
     <t>0.9609,0.0074,0.0110,0.0024</t>
   </si>
   <si>
-    <t>0.6937,0.1509,0.0544,0.0012</t>
+    <t>0.6935,0.1509,0.0544,0.0012</t>
   </si>
   <si>
     <t>0.9876,0.0014,0.0046,0.0002</t>
   </si>
   <si>
-    <t>0.9352,0.0419,0.0102,0.0027</t>
-  </si>
-  <si>
-    <t>0.0965,0.9050,0.0424,0.0072</t>
-  </si>
-  <si>
-    <t>0.9291,0.0123,0.0415,0.0008</t>
-  </si>
-  <si>
-    <t>0.8114,0.0258,0.1186,0.0019</t>
+    <t>0.9353,0.0419,0.0102,0.0027</t>
+  </si>
+  <si>
+    <t>0.0964,0.9051,0.0424,0.0072</t>
+  </si>
+  <si>
+    <t>0.9290,0.0123,0.0416,0.0008</t>
+  </si>
+  <si>
+    <t>0.8115,0.0258,0.1186,0.0019</t>
   </si>
   <si>
     <t>0.9934,0.0023,0.0010,0.0002</t>
@@ -1339,46 +1348,46 @@
     <t>0.9927,0.0010,0.0016,0.0004</t>
   </si>
   <si>
-    <t>0.6124,0.5039,0.0153,0.0018</t>
-  </si>
-  <si>
-    <t>0.4356,0.6960,0.0090,0.0014</t>
-  </si>
-  <si>
-    <t>0.8237,0.1902,0.0058,0.0013</t>
-  </si>
-  <si>
-    <t>0.7533,0.0400,0.1322,0.0011</t>
+    <t>0.6124,0.5038,0.0153,0.0018</t>
+  </si>
+  <si>
+    <t>0.4355,0.6961,0.0090,0.0014</t>
+  </si>
+  <si>
+    <t>0.8236,0.1902,0.0058,0.0013</t>
+  </si>
+  <si>
+    <t>0.7535,0.0400,0.1320,0.0011</t>
   </si>
   <si>
     <t>0.9911,0.0048,0.0012,0.0003</t>
   </si>
   <si>
-    <t>0.6268,0.2713,0.0501,0.0010</t>
+    <t>0.6263,0.2716,0.0502,0.0010</t>
   </si>
   <si>
     <t>0.9887,0.0020,0.0029,0.0003</t>
   </si>
   <si>
-    <t>0.9739,0.0208,0.0044,0.0009</t>
+    <t>0.9739,0.0207,0.0044,0.0009</t>
   </si>
   <si>
     <t>0.0062,0.0020,0.9939,0.0002</t>
   </si>
   <si>
-    <t>0.8671,0.0600,0.0414,0.0011</t>
+    <t>0.8671,0.0599,0.0415,0.0011</t>
   </si>
   <si>
     <t>0.0004,0.0004,0.9995,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.3434,0.9857,0.0017</t>
+    <t>0.0002,0.3442,0.9857,0.0017</t>
   </si>
   <si>
     <t>0.0148,0.0016,0.9861,0.0019</t>
   </si>
   <si>
-    <t>0.0015,0.6343,0.9146,0.0004</t>
+    <t>0.0015,0.6346,0.9145,0.0004</t>
   </si>
   <si>
     <t>0.0013,0.0014,0.9982,0.0001</t>
@@ -1390,28 +1399,28 @@
     <t>0.0071,0.0006,0.9948,0.0002</t>
   </si>
   <si>
-    <t>0.0806,0.0067,0.9330,0.0020</t>
+    <t>0.0805,0.0067,0.9330,0.0020</t>
   </si>
   <si>
     <t>0.1259,0.0017,0.9119,0.0007</t>
   </si>
   <si>
-    <t>0.4196,0.1646,0.3028,0.0093</t>
+    <t>0.4198,0.1647,0.3025,0.0093</t>
   </si>
   <si>
     <t>0.0250,0.0157,0.9629,0.0032</t>
   </si>
   <si>
-    <t>0.0113,0.0238,0.9755,0.0004</t>
-  </si>
-  <si>
-    <t>0.1008,0.0049,0.9131,0.0024</t>
-  </si>
-  <si>
-    <t>0.1047,0.0039,0.9184,0.0018</t>
-  </si>
-  <si>
-    <t>0.3804,0.0299,0.5773,0.0035</t>
+    <t>0.0113,0.0239,0.9754,0.0004</t>
+  </si>
+  <si>
+    <t>0.1009,0.0049,0.9130,0.0024</t>
+  </si>
+  <si>
+    <t>0.1048,0.0039,0.9184,0.0018</t>
+  </si>
+  <si>
+    <t>0.3805,0.0300,0.5771,0.0035</t>
   </si>
   <si>
     <t>0.3492,0.8369,0.0028,0.0000</t>
@@ -1420,37 +1429,37 @@
     <t>0.0072,0.9958,0.0022,0.0002</t>
   </si>
   <si>
-    <t>0.1240,0.9294,0.0073,0.0007</t>
-  </si>
-  <si>
-    <t>0.9639,0.0242,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.5960,0.5351,0.0031,0.0004</t>
-  </si>
-  <si>
-    <t>0.1284,0.9036,0.0111,0.0009</t>
-  </si>
-  <si>
-    <t>0.9421,0.0204,0.0161,0.0012</t>
-  </si>
-  <si>
-    <t>0.3522,0.0921,0.4969,0.0259</t>
-  </si>
-  <si>
-    <t>0.1748,0.0036,0.8502,0.0057</t>
-  </si>
-  <si>
-    <t>0.2837,0.0084,0.7067,0.0036</t>
+    <t>0.1239,0.9295,0.0074,0.0007</t>
+  </si>
+  <si>
+    <t>0.9640,0.0242,0.0038,0.0004</t>
+  </si>
+  <si>
+    <t>0.5961,0.5349,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.1286,0.9035,0.0111,0.0009</t>
+  </si>
+  <si>
+    <t>0.9420,0.0204,0.0161,0.0012</t>
+  </si>
+  <si>
+    <t>0.3521,0.0921,0.4969,0.0258</t>
+  </si>
+  <si>
+    <t>0.1747,0.0036,0.8502,0.0057</t>
+  </si>
+  <si>
+    <t>0.2834,0.0084,0.7071,0.0036</t>
   </si>
   <si>
     <t>0.0077,0.0007,0.9933,0.0004</t>
   </si>
   <si>
-    <t>0.0924,0.0066,0.9125,0.0020</t>
-  </si>
-  <si>
-    <t>0.0534,0.0267,0.9001,0.0016</t>
+    <t>0.0925,0.0066,0.9124,0.0020</t>
+  </si>
+  <si>
+    <t>0.0533,0.0267,0.9002,0.0016</t>
   </si>
   <si>
     <t>0.0051,0.0096,0.9926,0.0011</t>
@@ -1465,10 +1474,10 @@
     <t>0.9795,0.0118,0.0032,0.0015</t>
   </si>
   <si>
-    <t>0.9576,0.0227,0.0076,0.0030</t>
-  </si>
-  <si>
-    <t>0.9780,0.0206,0.0022,0.0013</t>
+    <t>0.9576,0.0227,0.0075,0.0030</t>
+  </si>
+  <si>
+    <t>0.9781,0.0206,0.0022,0.0013</t>
   </si>
   <si>
     <t>0.9749,0.0155,0.0035,0.0018</t>
@@ -1486,10 +1495,10 @@
     <t>0.0112,0.0007,0.9920,0.0004</t>
   </si>
   <si>
-    <t>0.0977,0.0581,0.8580,0.0020</t>
-  </si>
-  <si>
-    <t>0.3037,0.0141,0.6976,0.0089</t>
+    <t>0.0976,0.0581,0.8582,0.0020</t>
+  </si>
+  <si>
+    <t>0.3042,0.0141,0.6970,0.0089</t>
   </si>
   <si>
     <t>0.0008,0.0006,0.9992,0.0000</t>
@@ -1498,7 +1507,7 @@
     <t>0.0002,0.0038,0.9992,0.0003</t>
   </si>
   <si>
-    <t>0.0073,0.1275,0.9606,0.0007</t>
+    <t>0.0073,0.1277,0.9606,0.0007</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9999,0.0000</t>
@@ -1513,16 +1522,16 @@
     <t>0.0037,0.0131,0.9923,0.0009</t>
   </si>
   <si>
-    <t>0.0296,0.0379,0.9394,0.0040</t>
-  </si>
-  <si>
-    <t>0.7027,0.0053,0.2962,0.0034</t>
-  </si>
-  <si>
-    <t>0.7060,0.0015,0.2818,0.0034</t>
-  </si>
-  <si>
-    <t>0.9290,0.0114,0.0366,0.0006</t>
+    <t>0.0295,0.0378,0.9395,0.0040</t>
+  </si>
+  <si>
+    <t>0.7029,0.0053,0.2960,0.0034</t>
+  </si>
+  <si>
+    <t>0.7062,0.0015,0.2817,0.0034</t>
+  </si>
+  <si>
+    <t>0.9290,0.0114,0.0365,0.0006</t>
   </si>
   <si>
     <t>0.9909,0.0060,0.0006,0.0003</t>
@@ -1531,7 +1540,7 @@
     <t>0.9701,0.0381,0.0016,0.0005</t>
   </si>
   <si>
-    <t>0.9861,0.0084,0.0014,0.0006</t>
+    <t>0.9860,0.0084,0.0014,0.0006</t>
   </si>
   <si>
     <t>0.9339,0.0571,0.0063,0.0008</t>
@@ -1549,7 +1558,7 @@
     <t>0.9778,0.0082,0.0040,0.0013</t>
   </si>
   <si>
-    <t>0.0064,0.0737,0.9638,0.0011</t>
+    <t>0.0064,0.0738,0.9637,0.0011</t>
   </si>
   <si>
     <t>0.0012,0.0124,0.9977,0.0002</t>
@@ -1558,13 +1567,13 @@
     <t>0.0024,0.0039,0.9966,0.0001</t>
   </si>
   <si>
-    <t>0.0172,0.0969,0.9224,0.0009</t>
+    <t>0.0172,0.0972,0.9223,0.0009</t>
   </si>
   <si>
     <t>0.0083,0.0008,0.9941,0.0002</t>
   </si>
   <si>
-    <t>0.6880,0.0160,0.1041,0.0325</t>
+    <t>0.6875,0.0160,0.1041,0.0326</t>
   </si>
   <si>
     <t>0.1488,0.0061,0.8758,0.0053</t>
@@ -1588,7 +1597,7 @@
     <t>0.0001,0.0006,0.0006,0.9999</t>
   </si>
   <si>
-    <t>0.5572,0.0147,0.0085,0.2896</t>
+    <t>0.5576,0.0147,0.0085,0.2890</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +1983,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1988,7 +1997,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2002,7 +2011,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2016,7 +2025,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2030,7 +2039,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2044,7 +2053,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2058,7 +2067,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2072,7 +2081,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2086,7 +2095,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2100,7 +2109,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2114,7 +2123,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2128,7 +2137,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2142,7 +2151,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2156,7 +2165,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2170,7 +2179,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2184,7 +2193,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,10 +2204,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2209,10 +2218,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2223,10 +2232,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2237,10 +2246,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2251,10 +2260,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2265,10 +2274,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2282,7 +2291,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2296,7 +2305,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2310,7 +2319,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2324,7 +2333,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2338,7 +2347,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2352,7 +2361,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2366,7 +2375,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2380,7 +2389,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2394,7 +2403,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2408,7 +2417,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2422,7 +2431,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2436,7 +2445,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2450,7 +2459,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2461,10 +2470,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2475,10 +2484,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2489,10 +2498,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2506,7 +2515,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2520,7 +2529,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2534,7 +2543,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2545,10 +2554,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2559,10 +2568,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2576,7 +2585,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,10 +2596,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2601,10 +2610,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2615,10 +2624,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2629,10 +2638,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2646,7 +2655,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2660,7 +2669,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2674,7 +2683,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2688,7 +2697,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2702,7 +2711,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2716,7 +2725,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2730,7 +2739,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2744,7 +2753,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2758,7 +2767,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2772,7 +2781,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2786,7 +2795,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2800,7 +2809,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2814,7 +2823,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2825,10 +2834,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2842,7 +2851,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2856,7 +2865,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2867,10 +2876,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2884,7 +2893,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2895,10 +2904,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2909,10 +2918,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2926,7 +2935,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2940,7 +2949,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2954,7 +2963,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2965,10 +2974,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2979,10 +2988,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2993,10 +3002,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3007,10 +3016,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3024,7 +3033,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3038,7 +3047,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3052,7 +3061,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3066,7 +3075,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3080,7 +3089,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3094,7 +3103,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3105,10 +3114,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3119,10 +3128,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3133,10 +3142,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3147,10 +3156,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3161,10 +3170,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3175,10 +3184,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3192,7 +3201,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3206,7 +3215,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3220,7 +3229,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3234,7 +3243,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3248,7 +3257,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3262,7 +3271,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3276,7 +3285,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3290,7 +3299,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3304,7 +3313,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3318,7 +3327,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3332,7 +3341,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3346,7 +3355,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3360,7 +3369,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3374,7 +3383,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3388,7 +3397,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3402,7 +3411,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3416,7 +3425,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3430,7 +3439,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3444,7 +3453,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3458,7 +3467,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3469,10 +3478,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3483,10 +3492,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3497,10 +3506,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3511,10 +3520,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3525,10 +3534,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3539,10 +3548,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3556,7 +3565,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3570,7 +3579,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3584,7 +3593,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3598,7 +3607,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3612,7 +3621,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3623,10 +3632,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D120" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3637,10 +3646,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D121" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3651,10 +3660,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D122" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3665,10 +3674,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D123" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3679,10 +3688,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3693,10 +3702,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3707,10 +3716,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D126" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3721,10 +3730,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3738,7 +3747,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3752,7 +3761,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3766,7 +3775,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3780,7 +3789,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3794,7 +3803,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3808,7 +3817,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3822,7 +3831,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3836,7 +3845,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3847,10 +3856,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3861,10 +3870,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3878,7 +3887,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3892,7 +3901,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3906,7 +3915,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3917,10 +3926,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D141" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3934,7 +3943,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3948,7 +3957,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3962,7 +3971,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3976,7 +3985,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3990,7 +3999,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4004,7 +4013,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4015,10 +4024,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4032,7 +4041,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4043,10 +4052,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D150" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4060,7 +4069,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4071,10 +4080,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D152" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4088,7 +4097,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4102,7 +4111,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4116,7 +4125,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4130,7 +4139,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4144,7 +4153,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4158,7 +4167,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4172,7 +4181,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4186,7 +4195,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4200,7 +4209,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4211,10 +4220,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D162" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4228,7 +4237,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4242,7 +4251,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4256,7 +4265,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4270,7 +4279,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4284,7 +4293,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4298,7 +4307,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4312,7 +4321,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4326,7 +4335,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4340,7 +4349,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4354,7 +4363,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4365,10 +4374,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D173" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4379,10 +4388,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D174" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4396,7 +4405,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4410,7 +4419,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4424,7 +4433,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4438,7 +4447,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4452,7 +4461,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4466,7 +4475,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4480,7 +4489,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4494,7 +4503,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4508,7 +4517,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4522,7 +4531,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4536,7 +4545,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4547,10 +4556,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D186" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4564,7 +4573,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4578,7 +4587,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4592,7 +4601,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4606,7 +4615,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4620,7 +4629,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,10 +4640,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D192" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4648,7 +4657,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4662,7 +4671,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4676,7 +4685,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4690,7 +4699,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4704,7 +4713,7 @@
         <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4715,10 +4724,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D198" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4729,10 +4738,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4743,10 +4752,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D200" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4760,7 +4769,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4771,10 +4780,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D202" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4785,10 +4794,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D203" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4802,7 +4811,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,10 +4822,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D205" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4830,7 +4839,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4844,7 +4853,7 @@
         <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4858,7 +4867,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4872,7 +4881,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4886,7 +4895,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4900,7 +4909,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4914,7 +4923,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4928,7 +4937,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4942,7 +4951,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4956,7 +4965,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4970,7 +4979,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4984,7 +4993,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4998,7 +5007,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5012,7 +5021,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5026,7 +5035,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5040,7 +5049,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5054,7 +5063,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5068,7 +5077,7 @@
         <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5082,7 +5091,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5096,7 +5105,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5110,7 +5119,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5124,7 +5133,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5138,7 +5147,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5152,7 +5161,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5166,7 +5175,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5180,7 +5189,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5194,7 +5203,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5208,7 +5217,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5222,7 +5231,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5236,7 +5245,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5250,7 +5259,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5264,7 +5273,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5278,7 +5287,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5292,7 +5301,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5306,7 +5315,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5320,7 +5329,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5334,7 +5343,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5348,7 +5357,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5362,7 +5371,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5376,7 +5385,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5390,7 +5399,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5404,7 +5413,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5418,7 +5427,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5432,7 +5441,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5446,7 +5455,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5460,7 +5469,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5474,7 +5483,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5488,7 +5497,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5502,7 +5511,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5516,7 +5525,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5530,7 +5539,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
